--- a/results/0916-all/黄淮平原农业区/tech_selected_summary.xlsx
+++ b/results/0916-all/黄淮平原农业区/tech_selected_summary.xlsx
@@ -415,229 +415,229 @@
     <t>周口开发区</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>技术67</t>
-  </si>
-  <si>
-    <t>技术68</t>
-  </si>
-  <si>
-    <t>技术69</t>
-  </si>
-  <si>
-    <t>技术70</t>
-  </si>
-  <si>
-    <t>技术71</t>
-  </si>
-  <si>
-    <t>技术72</t>
-  </si>
-  <si>
-    <t>技术73</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Tech67</t>
+  </si>
+  <si>
+    <t>Tech68</t>
+  </si>
+  <si>
+    <t>Tech69</t>
+  </si>
+  <si>
+    <t>Tech70</t>
+  </si>
+  <si>
+    <t>Tech71</t>
+  </si>
+  <si>
+    <t>Tech72</t>
+  </si>
+  <si>
+    <t>Tech73</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -778,7 +778,7 @@
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 363946815.57</t>
+    <t>363946815.57</t>
   </si>
   <si>
     <t>Frequent removal_beef cattle</t>
@@ -826,7 +826,7 @@
     <t>4R(Right rate)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 822736682.85</t>
+    <t>822736682.85</t>
   </si>
   <si>
     <t>Yucca extract_dairy</t>
@@ -838,25 +838,25 @@
     <t>EEF(NI)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 670419558.51</t>
+    <t>670419558.51</t>
   </si>
   <si>
     <t>Feedstock adjustment_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 453509650.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 449414234.65</t>
+    <t>453509650.10</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>449414234.65</t>
   </si>
   <si>
     <t>Physical additives_pig</t>
   </si>
   <si>
-    <t>总经济成本: 474606137.43</t>
+    <t>474606137.43</t>
   </si>
   <si>
     <t>artificial film cover_pig</t>
@@ -868,7 +868,7 @@
     <t>Chemical amendments_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 502365245.98</t>
+    <t>502365245.98</t>
   </si>
   <si>
     <t>metal salt_Poultry</t>
@@ -880,19 +880,19 @@
     <t>Cover_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 580720907.93</t>
+    <t>580720907.93</t>
   </si>
   <si>
     <t>rolller press_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 513186893.96</t>
+    <t>513186893.96</t>
   </si>
   <si>
     <t>Urease Inhibitor_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 317497485.47</t>
+    <t>317497485.47</t>
   </si>
   <si>
     <t>Probiotics_pig</t>
@@ -928,22 +928,22 @@
     <t>cover crop (mix)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 1348278710.66</t>
+    <t>1348278710.66</t>
   </si>
   <si>
     <t>tillage management (zero tillage)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 338234893.53</t>
+    <t>338234893.53</t>
   </si>
   <si>
     <t>Biochar_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 239617347.42</t>
-  </si>
-  <si>
-    <t>总经济成本: 392496704.13</t>
+    <t>239617347.42</t>
+  </si>
+  <si>
+    <t>392496704.13</t>
   </si>
   <si>
     <t>EEF(DI)_rice</t>
@@ -955,22 +955,22 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 505899590.81</t>
+    <t>505899590.81</t>
   </si>
   <si>
     <t>tillage management (zero tillage)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 812454733.62</t>
-  </si>
-  <si>
-    <t>总经济成本: 396078634.35</t>
+    <t>812454733.62</t>
+  </si>
+  <si>
+    <t>396078634.35</t>
   </si>
   <si>
     <t>surface crust cover_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 515633066.82</t>
+    <t>515633066.82</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -985,7 +985,7 @@
     <t>cover crop (mix)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 679536669.92</t>
+    <t>679536669.92</t>
   </si>
   <si>
     <t>irrigation (drip irrigation)_maize</t>
@@ -994,22 +994,22 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 709681045.95</t>
-  </si>
-  <si>
-    <t>总经济成本: 858615633.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 352392047.33</t>
+    <t>709681045.95</t>
+  </si>
+  <si>
+    <t>858615633.35</t>
+  </si>
+  <si>
+    <t>352392047.33</t>
   </si>
   <si>
     <t>Urease Inhibitor_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 269245777.21</t>
-  </si>
-  <si>
-    <t>总经济成本: 245842194.27</t>
+    <t>269245777.21</t>
+  </si>
+  <si>
+    <t>245842194.27</t>
   </si>
   <si>
     <t>Zeolite_pig</t>
@@ -1021,7 +1021,7 @@
     <t>EEF(NI)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 335539710.98</t>
+    <t>335539710.98</t>
   </si>
   <si>
     <t>incorporation_dairy</t>
@@ -1033,10 +1033,10 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 512656342.76</t>
-  </si>
-  <si>
-    <t>总经济成本: 396325612.43</t>
+    <t>512656342.76</t>
+  </si>
+  <si>
+    <t>396325612.43</t>
   </si>
   <si>
     <t>rolller press_pig</t>
@@ -1048,124 +1048,124 @@
     <t>EEF(DI)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 905694587.37</t>
-  </si>
-  <si>
-    <t>总经济成本: 499907276.35</t>
+    <t>905694587.37</t>
+  </si>
+  <si>
+    <t>499907276.35</t>
   </si>
   <si>
     <t>compost（mid）30%-70%_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 541935386.49</t>
-  </si>
-  <si>
-    <t>总经济成本: 560808571.65</t>
-  </si>
-  <si>
-    <t>总经济成本: 374341991.17</t>
+    <t>541935386.49</t>
+  </si>
+  <si>
+    <t>560808571.65</t>
+  </si>
+  <si>
+    <t>374341991.17</t>
   </si>
   <si>
     <t>Oil_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 240382749.11</t>
+    <t>240382749.11</t>
   </si>
   <si>
     <t>Frequent removal_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 631735799.12</t>
-  </si>
-  <si>
-    <t>总经济成本: 362491642.96</t>
-  </si>
-  <si>
-    <t>总经济成本: 601679929.51</t>
-  </si>
-  <si>
-    <t>总经济成本: 833541631.16</t>
-  </si>
-  <si>
-    <t>总经济成本: 533281380.79</t>
-  </si>
-  <si>
-    <t>总经济成本: 192643167.98</t>
-  </si>
-  <si>
-    <t>总经济成本: 298873710.74</t>
+    <t>631735799.12</t>
+  </si>
+  <si>
+    <t>362491642.96</t>
+  </si>
+  <si>
+    <t>601679929.51</t>
+  </si>
+  <si>
+    <t>833541631.16</t>
+  </si>
+  <si>
+    <t>533281380.79</t>
+  </si>
+  <si>
+    <t>192643167.98</t>
+  </si>
+  <si>
+    <t>298873710.74</t>
   </si>
   <si>
     <t>Acidification_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 1040889093.47</t>
+    <t>1040889093.47</t>
   </si>
   <si>
     <t>Low protein diet_Pig</t>
   </si>
   <si>
-    <t>总经济成本: 1587443872.23</t>
-  </si>
-  <si>
-    <t>总经济成本: 1513643760.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 129415550.49</t>
-  </si>
-  <si>
-    <t>总经济成本: 612259982.47</t>
+    <t>1587443872.23</t>
+  </si>
+  <si>
+    <t>1513643760.75</t>
+  </si>
+  <si>
+    <t>129415550.49</t>
+  </si>
+  <si>
+    <t>612259982.47</t>
   </si>
   <si>
     <t>compost（low）≤30%_friut</t>
   </si>
   <si>
-    <t>总经济成本: 482172059.41</t>
+    <t>482172059.41</t>
   </si>
   <si>
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 459190270.81</t>
-  </si>
-  <si>
-    <t>总经济成本: 466904529.95</t>
-  </si>
-  <si>
-    <t>总经济成本: 488768265.09</t>
-  </si>
-  <si>
-    <t>总经济成本: 457161147.11</t>
-  </si>
-  <si>
-    <t>总经济成本: 1035457372.06</t>
+    <t>459190270.81</t>
+  </si>
+  <si>
+    <t>466904529.95</t>
+  </si>
+  <si>
+    <t>488768265.09</t>
+  </si>
+  <si>
+    <t>457161147.11</t>
+  </si>
+  <si>
+    <t>1035457372.06</t>
   </si>
   <si>
     <t>Decreasing grass maturity_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 916865238.38</t>
-  </si>
-  <si>
-    <t>总经济成本: 493743140.14</t>
-  </si>
-  <si>
-    <t>总经济成本: 631854525.59</t>
+    <t>916865238.38</t>
+  </si>
+  <si>
+    <t>493743140.14</t>
+  </si>
+  <si>
+    <t>631854525.59</t>
   </si>
   <si>
     <t>Plant-derived N substitution_maize</t>
   </si>
   <si>
-    <t>总经济成本: 373516126.46</t>
-  </si>
-  <si>
-    <t>总经济成本: 273387876.06</t>
-  </si>
-  <si>
-    <t>总经济成本: 387571276.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 1075143418.75</t>
+    <t>373516126.46</t>
+  </si>
+  <si>
+    <t>273387876.06</t>
+  </si>
+  <si>
+    <t>387571276.35</t>
+  </si>
+  <si>
+    <t>1075143418.75</t>
   </si>
   <si>
     <t>nitrification inhibitor_poultry</t>
@@ -1174,22 +1174,22 @@
     <t>cover crop (mix)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 863113897.90</t>
-  </si>
-  <si>
-    <t>总经济成本: 416393969.19</t>
-  </si>
-  <si>
-    <t>总经济成本: 340782942.11</t>
-  </si>
-  <si>
-    <t>总经济成本: 479647893.59</t>
-  </si>
-  <si>
-    <t>总经济成本: 588678087.81</t>
-  </si>
-  <si>
-    <t>总经济成本: 220269034.67</t>
+    <t>863113897.90</t>
+  </si>
+  <si>
+    <t>416393969.19</t>
+  </si>
+  <si>
+    <t>340782942.11</t>
+  </si>
+  <si>
+    <t>479647893.59</t>
+  </si>
+  <si>
+    <t>588678087.81</t>
+  </si>
+  <si>
+    <t>220269034.67</t>
   </si>
   <si>
     <t>Cover_poultry</t>
@@ -1201,64 +1201,64 @@
     <t>cover crop (non-leguminous)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 1043799056.63</t>
-  </si>
-  <si>
-    <t>总经济成本: 60748.58</t>
-  </si>
-  <si>
-    <t>总经济成本: 574654635.76</t>
+    <t>1043799056.63</t>
+  </si>
+  <si>
+    <t>60748.58</t>
+  </si>
+  <si>
+    <t>574654635.76</t>
   </si>
   <si>
     <t>nitrification inhibitor_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 648314902.48</t>
-  </si>
-  <si>
-    <t>总经济成本: 529102898.17</t>
-  </si>
-  <si>
-    <t>总经济成本: 149405814.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 234200409.52</t>
-  </si>
-  <si>
-    <t>总经济成本: 798647570.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 563462312.30</t>
-  </si>
-  <si>
-    <t>总经济成本: 279783430.21</t>
-  </si>
-  <si>
-    <t>总经济成本: 645215284.69</t>
-  </si>
-  <si>
-    <t>总经济成本: 402818144.66</t>
-  </si>
-  <si>
-    <t>总经济成本: 935207522.53</t>
+    <t>648314902.48</t>
+  </si>
+  <si>
+    <t>529102898.17</t>
+  </si>
+  <si>
+    <t>149405814.03</t>
+  </si>
+  <si>
+    <t>234200409.52</t>
+  </si>
+  <si>
+    <t>798647570.89</t>
+  </si>
+  <si>
+    <t>563462312.30</t>
+  </si>
+  <si>
+    <t>279783430.21</t>
+  </si>
+  <si>
+    <t>645215284.69</t>
+  </si>
+  <si>
+    <t>402818144.66</t>
+  </si>
+  <si>
+    <t>935207522.53</t>
   </si>
   <si>
     <t>biochar_maize</t>
   </si>
   <si>
-    <t>总经济成本: 405241309.55</t>
-  </si>
-  <si>
-    <t>总经济成本: 336458704.49</t>
-  </si>
-  <si>
-    <t>总经济成本: 531234140.34</t>
-  </si>
-  <si>
-    <t>总经济成本: 350043415.73</t>
-  </si>
-  <si>
-    <t>总经济成本: 930211009.20</t>
+    <t>405241309.55</t>
+  </si>
+  <si>
+    <t>336458704.49</t>
+  </si>
+  <si>
+    <t>531234140.34</t>
+  </si>
+  <si>
+    <t>350043415.73</t>
+  </si>
+  <si>
+    <t>930211009.20</t>
   </si>
   <si>
     <t>Urease Inhibitor_beef cattle</t>
@@ -1267,46 +1267,46 @@
     <t>manure（low）≤30%_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 179396460.11</t>
-  </si>
-  <si>
-    <t>总经济成本: 141990068.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 259585168.80</t>
+    <t>179396460.11</t>
+  </si>
+  <si>
+    <t>141990068.03</t>
+  </si>
+  <si>
+    <t>259585168.80</t>
   </si>
   <si>
     <t>band application_pig</t>
   </si>
   <si>
-    <t>总经济成本: 499324477.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 548018535.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 243838.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 235794121.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 229528085.49</t>
-  </si>
-  <si>
-    <t>总经济成本: 370287479.69</t>
-  </si>
-  <si>
-    <t>总经济成本: 288787672.11</t>
-  </si>
-  <si>
-    <t>总经济成本: 2328918497.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 638605318.21</t>
-  </si>
-  <si>
-    <t>总经济成本: 133429470.63</t>
+    <t>499324477.10</t>
+  </si>
+  <si>
+    <t>548018535.20</t>
+  </si>
+  <si>
+    <t>243838.50</t>
+  </si>
+  <si>
+    <t>235794121.10</t>
+  </si>
+  <si>
+    <t>229528085.49</t>
+  </si>
+  <si>
+    <t>370287479.69</t>
+  </si>
+  <si>
+    <t>288787672.11</t>
+  </si>
+  <si>
+    <t>2328918497.75</t>
+  </si>
+  <si>
+    <t>638605318.21</t>
+  </si>
+  <si>
+    <t>133429470.63</t>
   </si>
   <si>
     <t>Improving pasture management_sheep &amp; goat</t>
@@ -1366,34 +1366,34 @@
     <t>tillage management (reduced tillage)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 2405724664.05</t>
-  </si>
-  <si>
-    <t>总经济成本: 513846.26</t>
-  </si>
-  <si>
-    <t>总经济成本: 534386925.65</t>
+    <t>2405724664.05</t>
+  </si>
+  <si>
+    <t>513846.26</t>
+  </si>
+  <si>
+    <t>534386925.65</t>
   </si>
   <si>
     <t>surface applied  plus irrigation _sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 246066800.24</t>
+    <t>246066800.24</t>
   </si>
   <si>
     <t>Feedstock adjustment_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 684039936.26</t>
-  </si>
-  <si>
-    <t>总经济成本: 685615857.62</t>
-  </si>
-  <si>
-    <t>总经济成本: 547263260.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 436698181.20</t>
+    <t>684039936.26</t>
+  </si>
+  <si>
+    <t>685615857.62</t>
+  </si>
+  <si>
+    <t>547263260.89</t>
+  </si>
+  <si>
+    <t>436698181.20</t>
   </si>
   <si>
     <t>manure（high）≥70%_rice</t>
@@ -1402,10 +1402,10 @@
     <t>residue rerention_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 1732184641.28</t>
-  </si>
-  <si>
-    <t>总经济成本: 98630988.93</t>
+    <t>1732184641.28</t>
+  </si>
+  <si>
+    <t>98630988.93</t>
   </si>
 </sst>
 </file>
